--- a/skill/demo/demo1-data/memory_survey/Dati questionario finale.xlsx
+++ b/skill/demo/demo1-data/memory_survey/Dati questionario finale.xlsx
@@ -392,7 +392,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Et&lt;c3&gt;&lt;a0&gt;</t>
+          <t>Età</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
